--- a/astro-site/public/dl/seafood-restaurant-checklist-templates/BONUS-01-seafood-pre-shift-meeting-template.xlsx
+++ b/astro-site/public/dl/seafood-restaurant-checklist-templates/BONUS-01-seafood-pre-shift-meeting-template.xlsx
@@ -860,7 +860,7 @@
       <c r="C22" s="6" t="inlineStr"/>
       <c r="D22" s="6" t="inlineStr"/>
     </row>
-    <row r="23" ht="20" customHeight="1">
+    <row r="23" ht="41" customHeight="1">
       <c r="A23" s="5" t="inlineStr">
         <is>
           <t>Wine</t>
@@ -868,7 +868,7 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>Wine pick of the day (Albarino, Godello, Txakoli; 21+ with ID):</t>
+          <t>Wine pick of the day (Albariño, Sauvignon Blanc, Muscadet, Chablis; 21+ with ID):</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr"/>
